--- a/data/export/2026-09-19-浦东78路.xlsx
+++ b/data/export/2026-09-19-浦东78路.xlsx
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -637,27 +637,31 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：06:20采样，终点ETA 82分钟</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>1/9</t>
         </is>
       </c>
     </row>
@@ -723,24 +731,24 @@
       <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>06:45</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -748,35 +756,39 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -790,7 +802,7 @@
       <c r="T3" s="2" t="inlineStr"/>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
@@ -800,33 +812,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>2/9</t>
         </is>
       </c>
     </row>
@@ -834,7 +850,7 @@
       <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -844,7 +860,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -864,19 +880,19 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：07:20采样，终点ETA 51分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr"/>
@@ -887,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -901,7 +917,7 @@
       <c r="T4" s="2" t="inlineStr"/>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -916,7 +932,7 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
@@ -937,7 +953,911 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>3/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>1/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>2/9</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-浦东78路.xlsx
+++ b/data/export/2026-09-19-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC12"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -451,7 +451,7 @@
     <col width="20" customWidth="1" min="19" max="19"/>
     <col width="14" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
     <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -761,12 +761,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>07:58</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/9</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -892,10 +892,14 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：07:20采样，终点ETA 51分钟</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -903,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -927,33 +931,37 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,14 +1065,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
           <t>82.0</t>
@@ -1072,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/9</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1110,19 +1118,19 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：08:00采样，终点ETA 50分钟</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr"/>
@@ -1133,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1162,7 +1170,7 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
@@ -1172,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1183,7 +1191,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1216,27 +1224,31 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -1244,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1268,17 +1280,17 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -1288,13 +1300,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1405,7 +1421,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1520,7 +1536,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1597,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1631,7 +1647,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1708,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1742,7 +1758,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1750,22 +1766,22 @@
       <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1798,12 +1814,12 @@
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1852,12 +1868,575 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>2/9</t>
+          <t>5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>4/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>终点确认到达+2分钟（覆盖计划时间）</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-浦东78路.xlsx
+++ b/data/export/2026-09-19-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -451,7 +451,7 @@
     <col width="20" customWidth="1" min="19" max="19"/>
     <col width="14" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
     <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>2/12</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>5/12</t>
         </is>
       </c>
     </row>
@@ -999,24 +999,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
@@ -1118,19 +1118,19 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>101分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:00采样，终点ETA 50分钟</t>
+          <t>SHMAAS末次终点ETA推算：08:20采样，终点ETA 21分钟</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr"/>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1185,13 +1185,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>6/12</t>
         </is>
       </c>
     </row>
@@ -1229,12 +1233,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
@@ -1256,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,22 +1299,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
@@ -1348,19 +1352,19 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：08:20采样，终点ETA 55分钟</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr"/>
@@ -1371,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1400,7 +1404,7 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
@@ -1421,7 +1425,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1536,7 +1540,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1601,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1647,7 +1651,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1712,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1758,7 +1762,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1819,7 +1823,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1873,7 +1877,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>5/12</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1938,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1988,7 +1992,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>2/12</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2053,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2099,7 +2103,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2164,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2209,12 +2213,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
@@ -2275,7 +2279,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2325,7 +2329,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2347,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2386,7 +2390,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2405,7 +2409,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>终点确认到达+2分钟（覆盖计划时间）</t>
+          <t>计划发车</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2430,13 +2434,243 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>6/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>4/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr"/>
-      <c r="AC17" s="2" t="inlineStr">
-        <is>
-          <t>—/11</t>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-浦东78路.xlsx
+++ b/data/export/2026-09-19-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -451,7 +451,7 @@
     <col width="20" customWidth="1" min="19" max="19"/>
     <col width="14" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
     <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/12</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1113,27 +1113,31 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:20采样，终点ETA 21分钟</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -1141,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1165,12 +1169,12 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
@@ -1190,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1249,12 @@
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1260,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1314,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1347,27 +1351,31 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:20采样，终点ETA 55分钟</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1375,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1399,33 +1407,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1458,27 +1470,31 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -1486,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1510,37 +1526,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1573,27 +1589,31 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -1601,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1625,33 +1645,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1684,27 +1708,31 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -1712,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1736,33 +1764,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1795,27 +1827,31 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -1823,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1847,37 +1883,37 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>5/12</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1915,19 +1951,19 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：09:20采样，终点ETA 23分钟</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr"/>
@@ -1938,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1962,37 +1998,37 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2103,7 +2139,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2141,19 +2177,19 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>105分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：09:20采样，终点ETA 55分钟</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr"/>
@@ -2164,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2193,7 +2229,7 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
@@ -2218,7 +2254,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2329,7 +2365,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2426,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2439,12 +2475,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2541,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2559,7 +2595,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2656,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2670,7 +2706,919 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>78.5</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>终点确认到达+2分钟（覆盖计划时间）</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-浦东78路.xlsx
+++ b/data/export/2026-09-19-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:AC35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="20" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1951,19 +1951,19 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：09:20采样，终点ETA 23分钟</t>
+          <t>SHMAAS末次终点ETA推算：09:30采样，终点ETA 20分钟</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr"/>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
@@ -2023,12 +2023,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -2061,27 +2061,31 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -2089,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2113,33 +2117,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2177,19 +2185,19 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>105分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：09:20采样，终点ETA 55分钟</t>
+          <t>SHMAAS末次终点ETA推算：09:50采样，终点ETA 8分钟</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr"/>
@@ -2200,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2224,37 +2232,37 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2287,27 +2295,31 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -2315,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2339,33 +2351,37 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2398,27 +2414,31 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -2426,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2450,17 +2470,17 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -2470,17 +2490,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2518,19 +2538,19 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：10:20采样，终点ETA 6分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr"/>
@@ -2541,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2565,37 +2585,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2628,27 +2648,31 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -2656,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2680,33 +2704,37 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2744,19 +2772,19 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：10:20采样，终点ETA 7分钟</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr"/>
@@ -2767,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2791,33 +2819,37 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2855,19 +2887,19 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：10:20采样，终点ETA 18分钟</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr"/>
@@ -2878,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2902,33 +2934,37 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2966,19 +3002,19 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：10:20采样，终点ETA 13分钟</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr"/>
@@ -2989,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3013,17 +3049,17 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -3033,17 +3069,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3158,7 +3194,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3196,22 +3232,26 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>10:20采样：该车到重点站张杨北路博兴路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数20分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -3219,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3243,37 +3283,37 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3281,22 +3321,22 @@
       <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -3329,12 +3369,12 @@
       <c r="M25" s="2" t="inlineStr"/>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3348,12 +3388,12 @@
       <c r="T25" s="2" t="inlineStr"/>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>终点确认到达+2分钟（覆盖计划时间）</t>
+          <t>计划发车</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3373,22 +3413,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3396,22 +3436,22 @@
       <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3444,12 +3484,12 @@
       <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3463,12 +3503,12 @@
       <c r="T26" s="2" t="inlineStr"/>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>计划发车</t>
+          <t>终点确认到达+2分钟（覆盖计划时间）</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3488,22 +3528,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3604,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3618,7 +3658,931 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>77分钟</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>10:20采样：该车到重点站金高路行泰路 ETA 20分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>终点确认到达+2分钟（覆盖计划时间）</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>终点确认到达+2分钟（覆盖计划时间）</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>78.3</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-浦东78路.xlsx
+++ b/data/export/2026-09-19-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC35"/>
+  <dimension ref="A1:AC42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2013,22 +2013,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,17 +2132,17 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,22 +2366,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2887,19 +2887,19 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：10:20采样，终点ETA 18分钟</t>
+          <t>SHMAAS末次终点ETA推算：10:40采样，终点ETA 4分钟</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr"/>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -2997,27 +2997,31 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：10:20采样，终点ETA 13分钟</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3025,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3049,12 +3053,12 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
@@ -3064,22 +3068,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3112,27 +3116,31 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -3140,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3164,17 +3172,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3184,17 +3192,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3227,24 +3235,24 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站张杨北路博兴路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数20分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3259,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3283,12 +3291,12 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
@@ -3308,7 +3316,7 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3351,19 +3359,19 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：11:10采样，终点ETA 1分钟</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr"/>
@@ -3374,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3398,37 +3406,37 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3461,27 +3469,31 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3489,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3513,37 +3525,37 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3576,27 +3588,31 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -3604,7 +3620,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3628,37 +3644,37 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3691,29 +3707,29 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站金高路行泰路 ETA 20分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3723,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3747,12 +3763,12 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
@@ -3772,12 +3788,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3815,19 +3831,19 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：11:20采样，终点ETA 16分钟</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr"/>
@@ -3838,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3862,37 +3878,37 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3930,19 +3946,19 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：11:20采样，终点ETA 24分钟</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr"/>
@@ -3953,7 +3969,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3977,32 +3993,32 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4068,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4122,7 +4138,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4130,22 +4146,22 @@
       <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4178,12 +4194,12 @@
       <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4222,7 +4238,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4232,12 +4248,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4245,22 +4261,22 @@
       <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4293,12 +4309,12 @@
       <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4317,7 +4333,7 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>计划发车</t>
+          <t>终点确认到达+2分钟（覆盖计划时间）</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4347,12 +4363,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4429,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4462,7 +4478,7 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4528,7 +4544,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4582,7 +4598,812 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>终点确认到达+2分钟（覆盖计划时间）</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>83.5</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>77.5</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
           <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>83.7</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>84.3</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-浦东78路.xlsx
+++ b/data/export/2026-09-19-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC42"/>
+  <dimension ref="A1:AC48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="20" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,14 +1184,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
           <t>85.0</t>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2013,22 +2013,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2485,14 +2485,14 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>85.0</t>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2605,17 +2605,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2834,14 +2834,14 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
           <t>77.0</t>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2949,22 +2949,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3068,22 +3068,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3311,17 +3311,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3426,17 +3426,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3540,22 +3540,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3793,7 +3793,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3826,27 +3826,31 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：11:20采样，终点ETA 16分钟</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -3854,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3878,12 +3882,12 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
@@ -3903,12 +3907,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3941,27 +3945,31 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：11:20采样，终点ETA 24分钟</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -3969,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3993,12 +4001,12 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
@@ -4018,12 +4026,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4056,27 +4064,31 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -4084,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4108,17 +4120,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4128,17 +4140,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4171,27 +4183,31 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -4199,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4223,17 +4239,17 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
@@ -4243,17 +4259,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4286,27 +4302,31 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -4314,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4338,37 +4358,37 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4401,27 +4421,31 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -4429,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4453,17 +4477,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4473,17 +4497,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4516,27 +4540,31 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>08:31</t>
@@ -4544,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4568,29 +4596,29 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
           <t>77.0</t>
@@ -4598,7 +4626,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -4631,27 +4659,31 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -4659,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4683,17 +4715,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4703,17 +4735,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4751,19 +4783,19 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：12:20采样，终点ETA 29分钟</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr"/>
@@ -4774,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4798,37 +4830,37 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4889,7 +4921,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4943,7 +4975,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5004,7 +5036,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5053,12 +5085,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5096,19 +5128,19 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：12:20采样，终点ETA 53分钟</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr"/>
@@ -5119,7 +5151,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5148,7 +5180,7 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
@@ -5158,22 +5190,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5266,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5278,17 +5310,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5349,7 +5381,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5398,12 +5430,702 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>79.7</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>78分钟</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>82.8</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-浦东78路.xlsx
+++ b/data/export/2026-09-19-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC48"/>
+  <dimension ref="A1:AC52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="20" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,14 +1065,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
           <t>85.3</t>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,14 +1660,14 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
           <t>86.0</t>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2137,17 +2137,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2247,14 +2247,14 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
           <t>85.3</t>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,22 +2366,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2839,17 +2839,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2949,22 +2949,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3187,14 +3187,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>86.0</t>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3431,12 +3431,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3778,14 +3778,14 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
           <t>85.3</t>
@@ -3793,7 +3793,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3897,22 +3897,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4021,17 +4021,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4259,17 +4259,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4373,22 +4373,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4507,7 +4507,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4616,17 +4616,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4664,24 +4664,24 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4778,27 +4778,31 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：12:20采样，终点ETA 29分钟</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -4806,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4830,12 +4834,12 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
@@ -4855,12 +4859,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4893,27 +4897,31 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -4921,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4945,17 +4953,17 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4965,12 +4973,12 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5008,27 +5016,31 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -5036,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5060,17 +5072,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5080,17 +5092,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5123,7 +5135,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -5140,10 +5152,14 @@
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：12:20采样，终点ETA 53分钟</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5151,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5175,17 +5191,17 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5195,7 +5211,7 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
@@ -5205,7 +5221,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5238,27 +5254,31 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -5266,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5290,17 +5310,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5310,17 +5330,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -5358,19 +5378,19 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：13:20采样，终点ETA 25分钟</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr"/>
@@ -5381,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5405,37 +5425,37 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -5473,19 +5493,19 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：13:20采样，终点ETA 38分钟</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr"/>
@@ -5496,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5520,17 +5540,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5540,17 +5560,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5588,19 +5608,19 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：13:20采样，终点ETA 40分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr"/>
@@ -5611,7 +5631,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5635,37 +5655,37 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5746,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5775,12 +5795,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5841,7 +5861,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5956,7 +5976,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6000,7 +6020,7 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
@@ -6010,7 +6030,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6071,7 +6091,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6125,7 +6145,467 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>终点确认到达+2分钟（覆盖计划时间）</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>86.3</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>85.3</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-浦东78路.xlsx
+++ b/data/export/2026-09-19-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC52"/>
+  <dimension ref="A1:AC54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2023,12 +2023,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5378,19 +5378,19 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：13:20采样，终点ETA 25分钟</t>
+          <t>SHMAAS末次终点ETA推算：13:40采样，终点ETA 3分钟</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr"/>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
@@ -5450,12 +5450,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5488,27 +5488,31 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：13:20采样，终点ETA 38分钟</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>08:31</t>
@@ -5516,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5540,12 +5544,12 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
@@ -5565,12 +5569,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5603,7 +5607,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -5620,10 +5624,14 @@
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：13:20采样，终点ETA 40分钟</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -5631,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5655,12 +5663,12 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
@@ -5718,27 +5726,31 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5746,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5770,17 +5782,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5790,12 +5802,12 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5861,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5900,7 +5912,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5949,19 +5961,19 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±5分钟</t>
+          <t>13:40采样：该车到重点站五莲路凌河路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
@@ -5976,7 +5988,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6005,7 +6017,7 @@
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
@@ -6025,12 +6037,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6103,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6163,7 +6175,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -6206,7 +6218,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6255,12 +6267,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -6321,7 +6333,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6436,7 +6448,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6551,7 +6563,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6605,7 +6617,233 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>81.7</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr"/>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-浦东78路.xlsx
+++ b/data/export/2026-09-19-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC54"/>
+  <dimension ref="A1:AC58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2013,22 +2013,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2247,22 +2247,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3068,22 +3068,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3540,22 +3540,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3778,22 +3778,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4507,7 +4507,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4849,22 +4849,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5206,22 +5206,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5731,24 +5731,24 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5797,22 +5797,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5845,27 +5845,31 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
@@ -5873,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5897,17 +5901,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5917,13 +5921,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB46" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -5956,29 +5964,29 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>13:40采样：该车到重点站五莲路凌河路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5988,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6012,12 +6020,12 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
@@ -6027,22 +6035,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -6080,19 +6088,19 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：14:20采样，终点ETA 35分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr"/>
@@ -6103,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6127,27 +6135,27 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
@@ -6218,7 +6226,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6333,7 +6341,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6372,22 +6380,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6456,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6497,12 +6505,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -6563,7 +6571,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6678,7 +6686,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6793,7 +6801,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6837,13 +6845,489 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB54" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>82.8</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>86.3</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>15/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-浦东78路.xlsx
+++ b/data/export/2026-09-19-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC58"/>
+  <dimension ref="A1:AC64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2023,12 +2023,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,14 +2132,14 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>85.7</t>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,22 +2366,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2719,14 +2719,14 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
           <t>78.3</t>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3187,22 +3187,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3421,22 +3421,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3897,22 +3897,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4016,14 +4016,14 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
           <t>85.7</t>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4254,14 +4254,14 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
           <t>78.3</t>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4378,17 +4378,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4507,7 +4507,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4730,22 +4730,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5087,14 +5087,14 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
           <t>85.7</t>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5325,14 +5325,14 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
           <t>78.3</t>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5440,22 +5440,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5574,7 +5574,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5683,17 +5683,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5807,7 +5807,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5921,17 +5921,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6045,12 +6045,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -6088,19 +6088,19 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：14:20采样，终点ETA 35分钟</t>
+          <t>SHMAAS末次终点ETA推算：14:50采样，终点ETA 9分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr"/>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
@@ -6160,12 +6160,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -6198,27 +6198,31 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -6226,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6250,37 +6254,37 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6313,27 +6317,31 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6341,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6365,17 +6373,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6385,7 +6393,7 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
@@ -6395,7 +6403,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -6428,27 +6436,31 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -6456,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6480,17 +6492,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6500,17 +6512,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -6543,27 +6555,31 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -6571,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6595,37 +6611,37 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -6663,19 +6679,19 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：15:20采样，终点ETA 31分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr"/>
@@ -6686,7 +6702,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6710,37 +6726,37 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -6773,27 +6789,31 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
@@ -6801,7 +6821,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6825,17 +6845,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6845,17 +6865,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6893,19 +6913,19 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±5分钟</t>
+          <t>15:20采样：该车到重点站巨峰路成园路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -6920,7 +6940,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6949,7 +6969,7 @@
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
@@ -6969,7 +6989,7 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -6982,24 +7002,24 @@
       <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -7012,30 +7032,34 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>15:20采样：该车到重点站金高路俱进路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7049,7 +7073,7 @@
       <c r="T56" s="2" t="inlineStr"/>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
@@ -7059,37 +7083,37 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -7097,24 +7121,24 @@
       <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -7127,34 +7151,30 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±9分钟</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7168,37 +7188,37 @@
       <c r="T57" s="2" t="inlineStr"/>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>计划发车</t>
+          <t>终点确认到达+2分钟（覆盖计划时间）</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
@@ -7216,24 +7236,24 @@
       <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>沪A58633D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -7246,34 +7266,30 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7287,47 +7303,749 @@
       <c r="T58" s="2" t="inlineStr"/>
       <c r="U58" s="2" t="inlineStr">
         <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>85.7</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
           <t>15:20</t>
         </is>
       </c>
-      <c r="V58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W58" s="2" t="inlineStr">
+      <c r="W59" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X58" s="2" t="inlineStr">
+      <c r="X59" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y58" s="2" t="inlineStr">
+      <c r="Y59" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z58" s="2" t="inlineStr">
+      <c r="Z59" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB58" s="2" t="inlineStr">
-        <is>
-          <t>85.0</t>
-        </is>
-      </c>
-      <c r="AC58" s="2" t="inlineStr">
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>78.3</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>84.3</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
         <is>
           <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>84.2</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>83.7</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>81.2</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-浦东78路.xlsx
+++ b/data/export/2026-09-19-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC64"/>
+  <dimension ref="A1:AC73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2013,22 +2013,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2490,17 +2490,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2719,17 +2719,17 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2949,22 +2949,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3068,22 +3068,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3197,12 +3197,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3306,17 +3306,17 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3431,12 +3431,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3540,22 +3540,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3659,22 +3659,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3788,12 +3788,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4016,22 +4016,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4254,17 +4254,17 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4373,22 +4373,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4492,17 +4492,17 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4849,22 +4849,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4968,22 +4968,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5206,22 +5206,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5325,17 +5325,17 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5797,22 +5797,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5916,22 +5916,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6035,22 +6035,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6155,17 +6155,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6398,12 +6398,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6507,22 +6507,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6560,24 +6560,24 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6636,12 +6636,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -6674,27 +6674,31 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：15:20采样，终点ETA 31分钟</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -6702,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6726,12 +6730,12 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
@@ -6751,12 +6755,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -6794,24 +6798,24 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6821,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6860,22 +6864,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -6908,29 +6912,29 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>15:20采样：该车到重点站巨峰路成园路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6940,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6964,12 +6968,12 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
@@ -6979,22 +6983,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -7032,26 +7036,22 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>15:20采样：该车到重点站金高路俱进路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：16:20采样，终点ETA 10分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
@@ -7098,22 +7098,22 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -7146,27 +7146,31 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -7174,7 +7178,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7198,17 +7202,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7218,17 +7222,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -7266,19 +7270,19 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：16:20采样，终点ETA 26分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr"/>
@@ -7289,7 +7293,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7313,37 +7317,37 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -7376,29 +7380,29 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7408,7 +7412,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7432,12 +7436,12 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
@@ -7457,12 +7461,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -7523,7 +7527,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7562,17 +7566,17 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7638,7 +7642,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7687,12 +7691,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -7730,19 +7734,19 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±5分钟</t>
+          <t>16:20采样：该车到重点站五莲路归昌路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
@@ -7757,7 +7761,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7786,7 +7790,7 @@
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
@@ -7806,7 +7810,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7872,7 +7876,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7926,7 +7930,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -7964,19 +7968,19 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±5分钟</t>
+          <t>16:20采样：该车到重点站五莲路凌河路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
@@ -7991,7 +7995,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8020,32 +8024,1095 @@
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>16:20采样：该车到重点站金高路东靖路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>82.2</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>81.7</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>16:20采样：该车到重点站五莲路凌河路 ETA 27分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>84.3</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y64" s="2" t="inlineStr">
+      <c r="Y69" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z64" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA64" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB64" s="2" t="inlineStr">
-        <is>
-          <t>81.2</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr">
-        <is>
-          <t>2/15</t>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>84.6</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>85.4</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>终点确认到达+2分钟（覆盖计划时间）</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>77分钟</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数77分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-浦东78路.xlsx
+++ b/data/export/2026-09-19-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC73"/>
+  <dimension ref="A1:AC82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,17 +1779,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2023,12 +2023,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2247,22 +2247,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,22 +2366,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2485,22 +2485,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2600,22 +2600,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2834,22 +2834,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2949,22 +2949,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3068,22 +3068,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3187,22 +3187,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3421,17 +3421,17 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3669,12 +3669,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3778,22 +3778,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3897,22 +3897,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4135,22 +4135,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4259,17 +4259,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4373,22 +4373,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4611,22 +4611,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4730,17 +4730,17 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4849,22 +4849,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4978,12 +4978,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5330,17 +5330,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5440,22 +5440,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5559,22 +5559,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5797,22 +5797,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6045,12 +6045,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6150,22 +6150,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -6349,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6388,22 +6388,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6507,22 +6507,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6626,22 +6626,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -6706,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6745,17 +6745,17 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6983,22 +6983,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7108,12 +7108,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7217,22 +7217,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -7270,19 +7270,19 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：16:20采样，终点ETA 26分钟</t>
+          <t>SHMAAS末次终点ETA推算：16:40采样，终点ETA 10分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr"/>
@@ -7293,7 +7293,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
@@ -7342,12 +7342,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -7385,12 +7385,12 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -7499,27 +7499,31 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -7527,7 +7531,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7551,17 +7555,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7571,17 +7575,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -7614,27 +7618,31 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -7642,7 +7650,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7666,37 +7674,37 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -7729,24 +7737,24 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站五莲路归昌路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
@@ -7761,7 +7769,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7785,12 +7793,12 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
@@ -7800,22 +7808,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -7848,27 +7856,31 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -7876,7 +7888,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7900,37 +7912,37 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -7963,12 +7975,12 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -7980,7 +7992,7 @@
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站五莲路凌河路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
@@ -7995,7 +8007,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8019,12 +8031,12 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
@@ -8034,17 +8046,17 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8082,7 +8094,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -8092,14 +8104,14 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站金高路东靖路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
@@ -8114,7 +8126,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8138,12 +8150,12 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
@@ -8153,22 +8165,22 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -8206,19 +8218,19 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：17:20采样，终点ETA 14分钟</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr"/>
@@ -8229,7 +8241,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8253,37 +8265,37 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -8321,26 +8333,22 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站五莲路凌河路 ETA 27分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±12分钟</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：17:20采样，终点ETA 26分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8348,7 +8356,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8377,7 +8385,7 @@
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
@@ -8387,22 +8395,22 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -8463,7 +8471,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8517,7 +8525,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -8555,19 +8563,19 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+          <t>17:20采样：该车到重点站金杨路金口路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数12分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
@@ -8582,7 +8590,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8611,7 +8619,7 @@
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
@@ -8631,12 +8639,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -8674,24 +8682,24 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±8分钟</t>
+          <t>17:20采样：该车到重点站金高路俱进路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8701,7 +8709,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8730,7 +8738,7 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
@@ -8750,12 +8758,12 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -8793,19 +8801,19 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±5分钟</t>
+          <t>17:20采样：该车到重点站巨峰路成园路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
@@ -8820,7 +8828,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8849,7 +8857,7 @@
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
@@ -8869,7 +8877,7 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8892,7 +8900,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -8912,24 +8920,24 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±9分钟</t>
+          <t>17:20采样：该车到重点站五莲路荷泽路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8939,7 +8947,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8968,7 +8976,7 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
@@ -8988,12 +8996,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -9001,24 +9009,24 @@
       <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -9031,19 +9039,19 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数77分钟估算，约±5分钟</t>
+          <t>17:20采样：该车到重点站金高路俱进路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
@@ -9053,12 +9061,12 @@
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9072,47 +9080,1118 @@
       <c r="T73" s="2" t="inlineStr"/>
       <c r="U73" s="2" t="inlineStr">
         <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="V73" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>18:18</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>17:20采样：该车到重点站巨峰路成园路 ETA 20分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W73" s="2" t="inlineStr">
+      <c r="W74" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X73" s="2" t="inlineStr">
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>79.6</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>18:33</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y73" s="2" t="inlineStr">
+      <c r="Y75" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z73" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA73" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB73" s="2" t="inlineStr">
-        <is>
-          <t>78.0</t>
-        </is>
-      </c>
-      <c r="AC73" s="2" t="inlineStr">
-        <is>
-          <t>1/15</t>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>83.7</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>18:36</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>17:20采样：该车到重点站金高路俱进路 ETA 23分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>18:42</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>84.2</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>18:49</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>86.2</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>81.7</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>19:04</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>82.6</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>19:06</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>82.3</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>19:23</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>84.6</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-浦东78路.xlsx
+++ b/data/export/2026-09-19-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC82"/>
+  <dimension ref="A1:AC84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2013,22 +2013,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3540,22 +3540,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3669,12 +3669,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4978,12 +4978,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5206,22 +5206,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5335,7 +5335,7 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5807,7 +5807,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5916,17 +5916,17 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6035,22 +6035,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6284,7 +6284,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6349,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6403,7 +6403,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6517,7 +6517,7 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6864,17 +6864,17 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7098,22 +7098,22 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -7293,7 +7293,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7342,12 +7342,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -7531,7 +7531,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7580,7 +7580,7 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7769,7 +7769,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -7888,7 +7888,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8007,7 +8007,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8213,27 +8213,31 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：17:20采样，终点ETA 14分钟</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>08:31</t>
@@ -8241,7 +8245,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8265,12 +8269,12 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
@@ -8290,7 +8294,7 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8328,27 +8332,31 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：17:20采样，终点ETA 26分钟</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8356,7 +8364,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8380,12 +8388,12 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
@@ -8405,7 +8413,7 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8448,19 +8456,19 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：17:30采样，终点ETA 9分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr"/>
@@ -8471,7 +8479,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8495,32 +8503,32 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8563,19 +8571,19 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站金杨路金口路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数12分钟，约±5分钟</t>
+          <t>17:30采样：该车到重点站金杨路云山路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数12分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
@@ -8590,7 +8598,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8639,12 +8647,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -8687,21 +8695,17 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站金高路俱进路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±6分钟</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：17:30采样，终点ETA 33分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8709,7 +8713,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8733,12 +8737,12 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
@@ -8748,22 +8752,22 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -8801,19 +8805,19 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站巨峰路成园路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±5分钟</t>
+          <t>17:30采样：该车到重点站金杨路云山路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数15分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
@@ -8828,7 +8832,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8877,7 +8881,7 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8920,24 +8924,24 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站五莲路荷泽路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±10分钟</t>
+          <t>17:30采样：该车到重点站金高路源华路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8947,7 +8951,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8996,12 +9000,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -9158,19 +9162,19 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站巨峰路成园路 ETA 20分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
+          <t>17:30采样：该车到重点站金高路源华路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
@@ -9185,7 +9189,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9234,7 +9238,7 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9304,7 +9308,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9358,7 +9362,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -9396,7 +9400,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -9408,7 +9412,7 @@
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站金高路俱进路 ETA 23分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
+          <t>17:30采样：该车到重点站金高路万安街 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
@@ -9423,7 +9427,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9477,7 +9481,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -9542,7 +9546,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9661,7 +9665,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9758,19 +9762,19 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±8分钟</t>
+          <t>17:30采样：该车到重点站云山路银山路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9780,7 +9784,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9809,7 +9813,7 @@
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
@@ -9829,7 +9833,7 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -9899,7 +9903,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9948,7 +9952,7 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10018,7 +10022,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10080,24 +10084,24 @@
       <c r="A82" s="2" t="inlineStr"/>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -10110,34 +10114,30 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10151,47 +10151,285 @@
       <c r="T82" s="2" t="inlineStr"/>
       <c r="U82" s="2" t="inlineStr">
         <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>79.3</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="V82" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>19:23</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W82" s="2" t="inlineStr">
+      <c r="W83" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X82" s="2" t="inlineStr">
+      <c r="X83" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y82" s="2" t="inlineStr">
+      <c r="Y83" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z82" s="2" t="inlineStr">
+      <c r="Z83" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA82" s="2" t="inlineStr">
+      <c r="AA83" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AB82" s="2" t="inlineStr">
-        <is>
-          <t>84.6</t>
-        </is>
-      </c>
-      <c r="AC82" s="2" t="inlineStr">
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>84.3</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
         <is>
           <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>87.9</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>15/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-浦东78路.xlsx
+++ b/data/export/2026-09-19-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC84"/>
+  <dimension ref="A1:AC92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2247,22 +2247,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,17 +2366,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2485,17 +2485,17 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2719,17 +2719,17 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3431,12 +3431,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3659,22 +3659,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3778,22 +3778,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3897,17 +3897,17 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4016,22 +4016,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4145,12 +4145,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4254,17 +4254,17 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4492,22 +4492,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4968,22 +4968,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5325,17 +5325,17 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5440,17 +5440,17 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6150,17 +6150,17 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6269,17 +6269,17 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6388,22 +6388,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6517,12 +6517,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6626,12 +6626,12 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6755,12 +6755,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6993,12 +6993,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7108,7 +7108,7 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7217,17 +7217,17 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7332,22 +7332,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -7531,7 +7531,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7570,17 +7570,17 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
@@ -7769,7 +7769,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7808,17 +7808,17 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7888,7 +7888,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -8007,7 +8007,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8299,7 +8299,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -8337,24 +8337,24 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8566,24 +8566,24 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>17:30采样：该车到重点站金杨路云山路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数12分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8622,12 +8622,12 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
@@ -8637,22 +8637,22 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -8685,27 +8685,31 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：17:30采样，终点ETA 33分钟</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8713,7 +8717,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8737,12 +8741,12 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
@@ -8762,7 +8766,7 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8800,24 +8804,24 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>17:30采样：该车到重点站金杨路云山路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数15分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
@@ -8832,7 +8836,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8856,12 +8860,12 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
@@ -8871,22 +8875,22 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -8924,26 +8928,22 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>17:30采样：该车到重点站金高路源华路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±6分钟</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：17:50采样，终点ETA 23分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
@@ -8990,22 +8990,22 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -9043,26 +9043,22 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站金高路俱进路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：18:00采样，终点ETA 17分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -9070,7 +9066,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9099,7 +9095,7 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
@@ -9109,17 +9105,17 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9162,26 +9158,22 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>17:30采样：该车到重点站金高路源华路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：18:10采样，终点ETA 8分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -9189,7 +9181,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9218,7 +9210,7 @@
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
@@ -9228,17 +9220,17 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9276,29 +9268,29 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -9308,7 +9300,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9332,12 +9324,12 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
@@ -9347,17 +9339,17 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9400,26 +9392,22 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>17:30采样：该车到重点站金高路万安街 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：18:20采样，终点ETA 15分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9427,7 +9415,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9456,7 +9444,7 @@
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
@@ -9466,22 +9454,22 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -9519,26 +9507,22 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：18:20采样，终点ETA 26分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -9546,7 +9530,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9570,12 +9554,12 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
@@ -9595,12 +9579,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -9638,26 +9622,22 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>18:49</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：18:20采样，终点ETA 26分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -9665,7 +9645,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9689,12 +9669,12 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
@@ -9704,12 +9684,12 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
@@ -9757,24 +9737,24 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>17:30采样：该车到重点站云山路银山路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±10分钟</t>
+          <t>18:20采样：该车到重点站花山路杨高北路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数12分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9784,7 +9764,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9833,12 +9813,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -9876,7 +9856,7 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -9888,12 +9868,12 @@
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±10分钟</t>
+          <t>18:20采样：该车到重点站金高路行泰路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9903,7 +9883,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9932,7 +9912,7 @@
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
@@ -9957,7 +9937,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -9995,19 +9975,19 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+          <t>18:20采样：该车到重点站五莲路归昌路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
@@ -10022,7 +10002,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10051,7 +10031,7 @@
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
@@ -10071,12 +10051,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -10137,7 +10117,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10229,24 +10209,24 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±5分钟</t>
+          <t>18:20采样：该车到重点站杨高北路航津路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -10256,7 +10236,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10285,7 +10265,7 @@
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
@@ -10305,12 +10285,12 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -10318,24 +10298,24 @@
       <c r="A84" s="2" t="inlineStr"/>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>18:10</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -10348,34 +10328,34 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:27</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±8分钟</t>
+          <t>18:20采样：该车到重点站张杨北路金桥路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10389,47 +10369,999 @@
       <c r="T84" s="2" t="inlineStr"/>
       <c r="U84" s="2" t="inlineStr">
         <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>84.7</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
           <t>18:10</t>
         </is>
       </c>
-      <c r="V84" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>19:36</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>18:20采样：该车到重点站金高路东靖路 ETA 28分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W84" s="2" t="inlineStr">
+      <c r="W85" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X84" s="2" t="inlineStr">
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>87.6</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>15/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>19:34</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>18:20采样：该车到重点站云山路灵山路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>82.3</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>19:49</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y84" s="2" t="inlineStr">
+      <c r="Y87" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z84" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA84" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AB84" s="2" t="inlineStr">
-        <is>
-          <t>87.9</t>
-        </is>
-      </c>
-      <c r="AC84" s="2" t="inlineStr">
-        <is>
-          <t>15/15</t>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>19:51</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>85.8</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>20:02</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>79.8</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>20:17</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>87.1</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>20:23</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>20:44</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>86.2</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-浦东78路.xlsx
+++ b/data/export/2026-09-19-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC92"/>
+  <dimension ref="A1:AC95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,17 +1303,17 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,17 +1779,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2600,17 +2600,17 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2949,22 +2949,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3421,17 +3421,17 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4135,17 +4135,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4373,22 +4373,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4730,17 +4730,17 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5807,7 +5807,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6507,22 +6507,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6745,17 +6745,17 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7108,7 +7108,7 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7342,7 +7342,7 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7699,7 +7699,7 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7769,7 +7769,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7888,7 +7888,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7927,17 +7927,17 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8007,7 +8007,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8046,17 +8046,17 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8165,22 +8165,22 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8647,7 +8647,7 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8885,12 +8885,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9000,7 +9000,7 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9300,7 +9300,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9502,27 +9502,31 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：18:20采样，终点ETA 26分钟</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -9530,7 +9534,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9554,12 +9558,12 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
@@ -9569,17 +9573,17 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9617,27 +9621,31 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：18:20采样，终点ETA 26分钟</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -9645,7 +9653,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9669,12 +9677,12 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
@@ -9694,7 +9702,7 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9732,7 +9740,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -9749,12 +9757,12 @@
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>18:20采样：该车到重点站花山路杨高北路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数12分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9764,7 +9772,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9788,12 +9796,12 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
@@ -9803,22 +9811,22 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -9856,19 +9864,19 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>18:20采样：该车到重点站金高路行泰路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
+          <t>18:31采样：该车到重点站杨高北路航津路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数23分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -9883,7 +9891,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9932,7 +9940,7 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -9970,29 +9978,29 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>18:20采样：该车到重点站五莲路归昌路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -10002,7 +10010,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10026,12 +10034,12 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
@@ -10041,17 +10049,17 @@
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10117,7 +10125,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10214,19 +10222,19 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>18:20采样：该车到重点站杨高北路航津路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±6分钟</t>
+          <t>18:40采样：该车到重点站巨峰路成园路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -10236,7 +10244,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10285,7 +10293,7 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
@@ -10328,24 +10336,24 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>19:27</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>18:20采样：该车到重点站张杨北路金桥路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±7分钟</t>
+          <t>18:40采样：该车到重点站巨峰路成园路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数45分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -10355,7 +10363,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10404,7 +10412,7 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
@@ -10447,19 +10455,19 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>18:20采样：该车到重点站金高路东靖路 ETA 28分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±6分钟</t>
+          <t>18:40采样：该车到重点站金高路俱进路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
@@ -10474,7 +10482,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10523,7 +10531,7 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
@@ -10566,24 +10574,24 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>18:20采样：该车到重点站云山路灵山路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±8分钟</t>
+          <t>18:40采样：该车到重点站巨峰路成园路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -10593,7 +10601,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10642,12 +10650,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -10685,24 +10693,24 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>19:49</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±9分钟</t>
+          <t>18:40采样：该车到重点站杨高北路夏碧路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -10712,7 +10720,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10741,7 +10749,7 @@
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
@@ -10761,7 +10769,7 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
@@ -10831,7 +10839,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10950,7 +10958,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11069,7 +11077,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11188,7 +11196,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11250,24 +11258,24 @@
       <c r="A92" s="2" t="inlineStr"/>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -11280,19 +11288,19 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±5分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±5分钟</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
@@ -11302,12 +11310,12 @@
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11356,12 +11364,369 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>20:44</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
           <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>20:52</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>81.6</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>21:01</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>81.9</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-浦东78路.xlsx
+++ b/data/export/2026-09-19-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC95"/>
+  <dimension ref="A1:AC99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2719,22 +2719,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3659,22 +3659,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4016,22 +4016,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4145,12 +4145,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4254,22 +4254,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4492,22 +4492,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4968,22 +4968,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5325,22 +5325,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5450,12 +5450,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5569,12 +5569,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5693,7 +5693,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6160,12 +6160,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6349,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7227,12 +7227,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -7293,7 +7293,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7332,22 +7332,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7570,22 +7570,22 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7699,7 +7699,7 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7769,7 +7769,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7818,12 +7818,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7888,7 +7888,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -8007,7 +8007,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8180,7 +8180,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8294,12 +8294,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8523,12 +8523,12 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8637,22 +8637,22 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -8836,7 +8836,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8875,22 +8875,22 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8990,22 +8990,22 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9115,12 +9115,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -9181,7 +9181,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9220,22 +9220,22 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -9300,7 +9300,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9583,12 +9583,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -9653,7 +9653,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9702,7 +9702,7 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9772,7 +9772,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -9859,29 +9859,29 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>18:31采样：该车到重点站杨高北路航津路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数23分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
@@ -9940,12 +9940,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -9995,12 +9995,12 @@
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -10097,27 +10097,31 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
@@ -10125,7 +10129,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10149,17 +10153,17 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
@@ -10169,12 +10173,12 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
@@ -10212,12 +10216,12 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
@@ -10229,7 +10233,7 @@
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>18:40采样：该车到重点站巨峰路成园路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
@@ -10244,7 +10248,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10268,12 +10272,12 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
@@ -10331,29 +10335,29 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>18:40采样：该车到重点站巨峰路成园路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数45分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -10363,7 +10367,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10387,12 +10391,12 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
@@ -10402,22 +10406,22 @@
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -10569,24 +10573,24 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>18:40采样：该车到重点站巨峰路成园路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -10601,7 +10605,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10625,12 +10629,12 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
@@ -10640,22 +10644,22 @@
       </c>
       <c r="Z86" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -10688,29 +10692,29 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>18:40采样：该车到重点站杨高北路夏碧路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -10720,7 +10724,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10744,12 +10748,12 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
@@ -10759,22 +10763,22 @@
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -10812,19 +10816,19 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>19:51</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±5分钟</t>
+          <t>19:20采样：该车到重点站杨高北路夏碧路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数25分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
@@ -10839,7 +10843,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10868,7 +10872,7 @@
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
@@ -10888,12 +10892,12 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -10931,19 +10935,19 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>115分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±5分钟</t>
+          <t>同车下一次反向发车20:40，减去该车自身同类时段历史终点停站中位数5分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
@@ -10958,7 +10962,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10987,7 +10991,7 @@
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
@@ -10997,22 +11001,22 @@
       </c>
       <c r="Z89" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -11050,7 +11054,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
@@ -11062,12 +11066,12 @@
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±9分钟</t>
+          <t>19:20采样：该车到重点站五莲路荷泽路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -11077,7 +11081,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11106,7 +11110,7 @@
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
@@ -11169,19 +11173,19 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±5分钟</t>
+          <t>19:20采样：该车到重点站金高路俱进路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
@@ -11196,7 +11200,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11225,7 +11229,7 @@
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
@@ -11245,12 +11249,12 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -11288,19 +11292,19 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±5分钟</t>
+          <t>19:20采样：该车到重点站金高路俱进路 ETA 29分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
@@ -11315,7 +11319,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11344,7 +11348,7 @@
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
@@ -11364,12 +11368,12 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -11407,19 +11411,19 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±5分钟</t>
+          <t>19:20采样：该车到重点站巨峰路成园路 ETA 31分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
@@ -11434,7 +11438,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11463,7 +11467,7 @@
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
@@ -11483,7 +11487,7 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
@@ -11553,7 +11557,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11607,7 +11611,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -11615,24 +11619,24 @@
       <c r="A95" s="2" t="inlineStr"/>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>19:40</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -11645,19 +11649,19 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±5分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±5分钟</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
@@ -11667,12 +11671,12 @@
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11686,47 +11690,523 @@
       <c r="T95" s="2" t="inlineStr"/>
       <c r="U95" s="2" t="inlineStr">
         <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>83.4</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
           <t>19:40</t>
         </is>
       </c>
-      <c r="V95" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>21:01</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W95" s="2" t="inlineStr">
+      <c r="W96" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X95" s="2" t="inlineStr">
+      <c r="X96" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y95" s="2" t="inlineStr">
+      <c r="Y96" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z95" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA95" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB95" s="2" t="inlineStr">
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
         <is>
           <t>81.9</t>
         </is>
       </c>
-      <c r="AC95" s="2" t="inlineStr">
-        <is>
-          <t>6/15</t>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>21:02</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>21:31</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>21:58</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>78分钟</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>84.3</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-浦东78路.xlsx
+++ b/data/export/2026-09-19-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC99"/>
+  <dimension ref="A1:AC103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2834,22 +2834,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3431,12 +3431,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4145,12 +4145,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4611,22 +4611,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5335,12 +5335,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5450,12 +5450,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5559,22 +5559,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5916,22 +5916,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6349,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6398,7 +6398,7 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6517,12 +6517,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6755,12 +6755,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6864,22 +6864,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7227,7 +7227,7 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7342,12 +7342,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7580,12 +7580,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7699,7 +7699,7 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7769,7 +7769,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7818,12 +7818,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -7888,7 +7888,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -8007,7 +8007,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8284,22 +8284,22 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8518,22 +8518,22 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -8598,7 +8598,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8652,7 +8652,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -8836,7 +8836,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9000,12 +9000,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -9300,7 +9300,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9583,12 +9583,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -9653,7 +9653,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9702,7 +9702,7 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9772,7 +9772,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9821,12 +9821,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -9891,7 +9891,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9930,22 +9930,22 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10059,12 +10059,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10168,22 +10168,22 @@
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -10367,7 +10367,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10421,7 +10421,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -10605,7 +10605,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10773,12 +10773,12 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -10811,29 +10811,29 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站杨高北路夏碧路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数25分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -10843,7 +10843,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
@@ -10892,7 +10892,7 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
@@ -10930,24 +10930,24 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>115分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车20:40，减去该车自身同类时段历史终点停站中位数5分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
@@ -10962,7 +10962,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
@@ -11011,12 +11011,12 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -11049,29 +11049,29 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站五莲路荷泽路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -11081,7 +11081,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
@@ -11130,7 +11130,7 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
@@ -11168,29 +11168,29 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站金高路俱进路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -11200,7 +11200,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
@@ -11249,12 +11249,12 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -11287,29 +11287,29 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站金高路俱进路 ETA 29分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -11319,7 +11319,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
@@ -11368,12 +11368,12 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -11406,29 +11406,29 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>20:36</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站巨峰路成园路 ETA 31分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
@@ -11530,19 +11530,19 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>20:52</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±5分钟</t>
+          <t>20:20采样：该车到重点站云山路灵山路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数16分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
@@ -11557,7 +11557,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11586,7 +11586,7 @@
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
@@ -11606,12 +11606,12 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -11676,7 +11676,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11730,7 +11730,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -11768,26 +11768,22 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：20:20采样，终点ETA 39分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -11795,7 +11791,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11819,12 +11815,12 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
@@ -11844,12 +11840,12 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -11914,7 +11910,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11976,24 +11972,24 @@
       <c r="A98" s="2" t="inlineStr"/>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>20:10</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -12006,34 +12002,34 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±6分钟</t>
+          <t>同车下一次反向发车21:10，减去该车自身同类时段历史终点停站中位数8分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12047,7 +12043,7 @@
       <c r="T98" s="2" t="inlineStr"/>
       <c r="U98" s="2" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="V98" s="2" t="inlineStr">
@@ -12062,7 +12058,7 @@
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
@@ -12082,12 +12078,12 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -12095,24 +12091,24 @@
       <c r="A99" s="2" t="inlineStr"/>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>20:40</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -12125,19 +12121,19 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>21:58</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±5分钟</t>
+          <t>同车下一次反向发车21:40，减去该车自身同类时段历史终点停站中位数10分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
@@ -12147,12 +12143,12 @@
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12166,47 +12162,523 @@
       <c r="T99" s="2" t="inlineStr"/>
       <c r="U99" s="2" t="inlineStr">
         <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>同车反向发车反推</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>21:29</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>20:20采样：该车到重点站五莲路凌河路 ETA 20分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>84.9</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
           <t>20:40</t>
         </is>
       </c>
-      <c r="V99" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>21:58</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>78分钟</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W99" s="2" t="inlineStr">
+      <c r="W101" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X99" s="2" t="inlineStr">
+      <c r="X101" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y99" s="2" t="inlineStr">
+      <c r="Y101" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z99" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA99" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB99" s="2" t="inlineStr">
-        <is>
-          <t>84.3</t>
-        </is>
-      </c>
-      <c r="AC99" s="2" t="inlineStr">
-        <is>
-          <t>9/15</t>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>78.3</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>22:31</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>81.1</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>22:59</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-浦东78路.xlsx
+++ b/data/export/2026-09-19-浦东78路.xlsx
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>84.9</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3197,12 +3197,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3431,12 +3431,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>84.9</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>84.9</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5335,7 +5335,7 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6517,7 +6517,7 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6636,12 +6636,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -6706,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6755,12 +6755,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -7293,7 +7293,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7342,12 +7342,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>84.9</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -7531,7 +7531,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7580,7 +7580,7 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7699,12 +7699,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -7888,7 +7888,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7937,7 +7937,7 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8007,7 +8007,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8245,7 +8245,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8528,12 +8528,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -8890,7 +8890,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9000,12 +9000,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>84.9</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -9181,7 +9181,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9940,7 +9940,7 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10059,12 +10059,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -10659,7 +10659,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -10724,7 +10724,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10773,12 +10773,12 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>84.9</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -10962,7 +10962,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11011,7 +11011,7 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
@@ -11292,12 +11292,12 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>20:36</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
@@ -11319,7 +11319,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
@@ -11411,24 +11411,24 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>20:36</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11487,12 +11487,12 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -11530,26 +11530,22 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站云山路灵山路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数16分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：20:30采样，终点ETA 13分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -11557,7 +11553,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11586,7 +11582,7 @@
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
@@ -11606,7 +11602,7 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
@@ -11763,27 +11759,31 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:20采样，终点ETA 39分钟</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -11791,7 +11791,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11815,12 +11815,12 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
@@ -11840,12 +11840,12 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -11964,7 +11964,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -11997,24 +11997,24 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车21:10，减去该车自身同类时段历史终点停站中位数8分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
@@ -12029,7 +12029,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12053,12 +12053,12 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
@@ -12116,29 +12116,29 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车21:40，减去该车自身同类时段历史终点停站中位数10分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -12148,7 +12148,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12172,12 +12172,12 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -12235,29 +12235,29 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>21:29</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站五莲路凌河路 ETA 20分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -12267,7 +12267,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12291,12 +12291,12 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
@@ -12316,12 +12316,12 @@
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>84.9</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -12354,29 +12354,29 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>21:58</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -12386,7 +12386,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
@@ -12435,7 +12435,7 @@
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
@@ -12478,24 +12478,24 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>22:26</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±7分钟</t>
+          <t>21:20采样：该车到重点站金杨路枣庄路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -12505,7 +12505,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12534,7 +12534,7 @@
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
@@ -12554,7 +12554,7 @@
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
@@ -12624,7 +12624,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12673,12 +12673,12 @@
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-19-浦东78路.xlsx
+++ b/data/export/2026-09-19-浦东78路.xlsx
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -8245,7 +8245,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9940,7 +9940,7 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10129,7 +10129,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10962,7 +10962,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -12029,7 +12029,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
@@ -12148,7 +12148,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12197,7 +12197,7 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
@@ -12252,12 +12252,12 @@
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -12267,7 +12267,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12371,12 +12371,12 @@
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -12386,7 +12386,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12473,7 +12473,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -12483,19 +12483,19 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>21:20采样：该车到重点站金杨路枣庄路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -12505,7 +12505,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12529,12 +12529,12 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
@@ -12554,7 +12554,7 @@
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
@@ -12597,19 +12597,19 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>22:56</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±5分钟</t>
+          <t>21:50采样：该车到重点站金杨路云山路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
@@ -12624,7 +12624,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12653,7 +12653,7 @@
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
@@ -12673,7 +12673,7 @@
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
